--- a/system_development/V0.2/MOB-V0.2.xlsx
+++ b/system_development/V0.2/MOB-V0.2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adowney2\Documents\GitHub\Fieldable-NV-Center\system_development\V0.2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shari\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B75AD68-FAD2-4D98-9AF6-36C406C3DA58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16931E7F-AD2E-489D-97E5-1EAA1F157371}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="bill_of_materials" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>Individual Cost</t>
   </si>
@@ -81,6 +81,21 @@
   </si>
   <si>
     <t>Primary or Alternative Part</t>
+  </si>
+  <si>
+    <t>532 nm Diode-Pumped Solid State (DPSS) Lasers</t>
+  </si>
+  <si>
+    <t>DJ532-10</t>
+  </si>
+  <si>
+    <t>https://www.thorlabs.com/item/DJ532-10?aID=972dd12f8a3eb31bbd30b717692f2777&amp;aC=1</t>
+  </si>
+  <si>
+    <t>Primary</t>
+  </si>
+  <si>
+    <t>green laser diode</t>
   </si>
 </sst>
 </file>
@@ -173,7 +188,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -231,6 +246,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -570,24 +591,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6D3A36C-E8CE-4E50-A172-E48E2F9A45A8}">
   <dimension ref="A1:N22"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="27.28515625" customWidth="1"/>
-    <col min="3" max="3" width="37.85546875" customWidth="1"/>
-    <col min="4" max="4" width="20.7109375" customWidth="1"/>
-    <col min="5" max="5" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="1" max="1" width="29.88671875" customWidth="1"/>
+    <col min="2" max="2" width="27.33203125" customWidth="1"/>
+    <col min="3" max="3" width="42.33203125" customWidth="1"/>
+    <col min="4" max="4" width="20.6640625" customWidth="1"/>
+    <col min="5" max="5" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="27" customWidth="1"/>
     <col min="8" max="8" width="13" customWidth="1"/>
     <col min="9" max="9" width="79" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="45.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="83.42578125" customWidth="1"/>
-    <col min="12" max="12" width="62.42578125" customWidth="1"/>
-    <col min="13" max="13" width="55.85546875" customWidth="1"/>
+    <col min="10" max="10" width="45.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="83.44140625" customWidth="1"/>
+    <col min="12" max="12" width="62.44140625" customWidth="1"/>
+    <col min="13" max="13" width="55.88671875" customWidth="1"/>
     <col min="14" max="14" width="51" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>10</v>
       </c>
@@ -631,19 +653,35 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="17"/>
-      <c r="B2" s="17"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
+    <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="23">
+        <v>1</v>
+      </c>
+      <c r="F2" s="22">
+        <v>188.12</v>
+      </c>
+      <c r="G2" s="22">
+        <v>188.12</v>
+      </c>
       <c r="H2" s="5"/>
-      <c r="I2" s="1"/>
+      <c r="I2" s="1" t="s">
+        <v>17</v>
+      </c>
       <c r="K2" s="2"/>
     </row>
-    <row r="3" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="18"/>
       <c r="B3" s="17"/>
       <c r="C3" s="2"/>
@@ -655,7 +693,7 @@
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
     </row>
-    <row r="4" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="17"/>
       <c r="C4" s="16"/>
       <c r="D4" s="4"/>
@@ -668,7 +706,7 @@
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
     </row>
-    <row r="5" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="17"/>
       <c r="C5" s="16"/>
       <c r="D5" s="4"/>
@@ -681,7 +719,7 @@
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
     </row>
-    <row r="6" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="17"/>
       <c r="C6" s="2"/>
       <c r="D6" s="20"/>
@@ -691,7 +729,7 @@
       <c r="H6" s="5"/>
       <c r="I6" s="1"/>
     </row>
-    <row r="7" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="10"/>
       <c r="B7" s="17"/>
       <c r="C7" s="2"/>
@@ -703,7 +741,7 @@
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
     </row>
-    <row r="8" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="10"/>
       <c r="B8" s="17"/>
       <c r="C8" s="2"/>
@@ -715,7 +753,7 @@
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
     </row>
-    <row r="9" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="10"/>
       <c r="B9" s="10"/>
       <c r="C9" s="2"/>
@@ -727,7 +765,7 @@
       <c r="I9" s="1"/>
       <c r="J9" s="4"/>
     </row>
-    <row r="10" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="10"/>
       <c r="B10" s="17"/>
       <c r="C10" s="2"/>
@@ -739,7 +777,7 @@
       <c r="I10" s="1"/>
       <c r="J10" s="4"/>
     </row>
-    <row r="11" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="10"/>
       <c r="B11" s="17"/>
       <c r="C11" s="4"/>
@@ -751,7 +789,7 @@
       <c r="I11" s="1"/>
       <c r="J11" s="4"/>
     </row>
-    <row r="12" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="10"/>
       <c r="B12" s="17"/>
       <c r="C12" s="2"/>
@@ -763,7 +801,7 @@
       <c r="I12" s="1"/>
       <c r="J12" s="4"/>
     </row>
-    <row r="13" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="10"/>
       <c r="B13" s="17"/>
       <c r="C13" s="2"/>
@@ -775,7 +813,7 @@
       <c r="I13" s="1"/>
       <c r="J13" s="4"/>
     </row>
-    <row r="14" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="10"/>
       <c r="B14" s="17"/>
       <c r="C14" s="2"/>
@@ -787,7 +825,7 @@
       <c r="I14" s="1"/>
       <c r="J14" s="4"/>
     </row>
-    <row r="15" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="10"/>
       <c r="B15" s="17"/>
       <c r="C15" s="2"/>
@@ -798,7 +836,7 @@
       <c r="H15" s="5"/>
       <c r="I15" s="1"/>
     </row>
-    <row r="16" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="10"/>
       <c r="B16" s="10"/>
       <c r="C16" s="2"/>
@@ -810,7 +848,7 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
     </row>
-    <row r="17" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="10"/>
       <c r="B17" s="17"/>
       <c r="C17" s="2"/>
@@ -822,7 +860,7 @@
       <c r="I17" s="3"/>
       <c r="J17" s="4"/>
     </row>
-    <row r="18" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="11"/>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -835,7 +873,7 @@
       <c r="J18" s="11"/>
       <c r="K18" s="11"/>
     </row>
-    <row r="19" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="11"/>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -847,7 +885,7 @@
       <c r="J19" s="11"/>
       <c r="K19" s="11"/>
     </row>
-    <row r="20" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="4"/>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
@@ -858,17 +896,17 @@
       <c r="H20" s="4"/>
       <c r="I20" s="4"/>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="F21" s="8"/>
       <c r="G21" s="8"/>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="F22" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G22" s="5">
         <f>SUM(G2:G21)</f>
-        <v>0</v>
+        <v>188.12</v>
       </c>
     </row>
   </sheetData>
